--- a/data/nzd0166/nzd0166.xlsx
+++ b/data/nzd0166/nzd0166.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F376"/>
+  <dimension ref="A1:F377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9452,6 +9452,30 @@
         <v>360.13</v>
       </c>
       <c r="F376" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>335.35</v>
+      </c>
+      <c r="C377" t="n">
+        <v>335.98</v>
+      </c>
+      <c r="D377" t="n">
+        <v>333.22</v>
+      </c>
+      <c r="E377" t="n">
+        <v>355.85</v>
+      </c>
+      <c r="F377" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -9468,7 +9492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B395"/>
+  <dimension ref="A1:B396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13421,6 +13445,16 @@
       </c>
       <c r="B395" t="n">
         <v>-0.4</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>0.52</v>
       </c>
     </row>
   </sheetData>
@@ -13589,28 +13623,28 @@
         <v>0.0454</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01595143276881954</v>
+        <v>-0.01366414325852061</v>
       </c>
       <c r="J2" t="n">
+        <v>376</v>
+      </c>
+      <c r="K2" t="n">
         <v>375</v>
       </c>
-      <c r="K2" t="n">
-        <v>374</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0002133088247475712</v>
+        <v>0.0001573704727531045</v>
       </c>
       <c r="M2" t="n">
-        <v>5.90869930369398</v>
+        <v>5.90589763455503</v>
       </c>
       <c r="N2" t="n">
-        <v>62.22316104434559</v>
+        <v>62.10216808677433</v>
       </c>
       <c r="O2" t="n">
-        <v>7.888165885955087</v>
+        <v>7.880492883492398</v>
       </c>
       <c r="P2" t="n">
-        <v>331.6494367433911</v>
+        <v>331.6247741235168</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13667,28 +13701,28 @@
         <v>0.0572</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09705872029682495</v>
+        <v>-0.09100692490182237</v>
       </c>
       <c r="J3" t="n">
+        <v>376</v>
+      </c>
+      <c r="K3" t="n">
         <v>375</v>
       </c>
-      <c r="K3" t="n">
-        <v>374</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.006404586130036805</v>
+        <v>0.005646099726639875</v>
       </c>
       <c r="M3" t="n">
-        <v>7.353458952042904</v>
+        <v>7.357603817094079</v>
       </c>
       <c r="N3" t="n">
-        <v>76.25033848829906</v>
+        <v>76.36157294921173</v>
       </c>
       <c r="O3" t="n">
-        <v>8.732143980048603</v>
+        <v>8.738510911431749</v>
       </c>
       <c r="P3" t="n">
-        <v>327.6414689241368</v>
+        <v>327.5762156500269</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13745,28 +13779,28 @@
         <v>0.0697</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1956261130685981</v>
+        <v>-0.1917868546778442</v>
       </c>
       <c r="J4" t="n">
+        <v>376</v>
+      </c>
+      <c r="K4" t="n">
         <v>375</v>
       </c>
-      <c r="K4" t="n">
-        <v>374</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.04570362092523717</v>
+        <v>0.04413339862743204</v>
       </c>
       <c r="M4" t="n">
-        <v>5.027494275769625</v>
+        <v>5.032682401802552</v>
       </c>
       <c r="N4" t="n">
-        <v>41.69082269274063</v>
+        <v>41.70624950017011</v>
       </c>
       <c r="O4" t="n">
-        <v>6.456843090298898</v>
+        <v>6.458037588940631</v>
       </c>
       <c r="P4" t="n">
-        <v>331.4758016167042</v>
+        <v>331.4344049461629</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13823,28 +13857,28 @@
         <v>0.0265</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05517253429736117</v>
+        <v>-0.05644736584794184</v>
       </c>
       <c r="J5" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K5" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002550507348991427</v>
+        <v>0.002684960657080238</v>
       </c>
       <c r="M5" t="n">
-        <v>6.006997056851758</v>
+        <v>5.999554452561155</v>
       </c>
       <c r="N5" t="n">
-        <v>62.71133725116526</v>
+        <v>62.55871197597397</v>
       </c>
       <c r="O5" t="n">
-        <v>7.919049011792089</v>
+        <v>7.90940655017644</v>
       </c>
       <c r="P5" t="n">
-        <v>359.6324983553391</v>
+        <v>359.6461556335574</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13882,7 +13916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F376"/>
+  <dimension ref="A1:F377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25905,6 +25939,38 @@
         </is>
       </c>
     </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>-36.76407687026856,175.7506417713072</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>-36.764760886445174,175.75032315765452</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>-36.765483840429084,175.75004424003572</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>-36.76622730825634,175.75029056724216</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0166/nzd0166.xlsx
+++ b/data/nzd0166/nzd0166.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F377"/>
+  <dimension ref="A1:F378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9478,6 +9478,30 @@
       <c r="F377" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>335.48</v>
+      </c>
+      <c r="C378" t="n">
+        <v>336.08</v>
+      </c>
+      <c r="D378" t="n">
+        <v>333.74</v>
+      </c>
+      <c r="E378" t="n">
+        <v>357.95</v>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -9492,7 +9516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B396"/>
+  <dimension ref="A1:B397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13455,6 +13479,16 @@
       </c>
       <c r="B396" t="n">
         <v>0.52</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -13623,28 +13657,28 @@
         <v>0.0454</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01366414325852061</v>
+        <v>-0.01133053127086357</v>
       </c>
       <c r="J2" t="n">
+        <v>377</v>
+      </c>
+      <c r="K2" t="n">
         <v>376</v>
       </c>
-      <c r="K2" t="n">
-        <v>375</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0001573704727531045</v>
+        <v>0.0001087907615839878</v>
       </c>
       <c r="M2" t="n">
-        <v>5.90589763455503</v>
+        <v>5.903304906317227</v>
       </c>
       <c r="N2" t="n">
-        <v>62.10216808677433</v>
+        <v>61.98390774913079</v>
       </c>
       <c r="O2" t="n">
-        <v>7.880492883492398</v>
+        <v>7.872985948744656</v>
       </c>
       <c r="P2" t="n">
-        <v>331.6247741235168</v>
+        <v>331.5995447636176</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13701,28 +13735,28 @@
         <v>0.0572</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09100692490182237</v>
+        <v>-0.08496333241402673</v>
       </c>
       <c r="J3" t="n">
+        <v>377</v>
+      </c>
+      <c r="K3" t="n">
         <v>376</v>
       </c>
-      <c r="K3" t="n">
-        <v>375</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.005646099726639875</v>
+        <v>0.00493428165648746</v>
       </c>
       <c r="M3" t="n">
-        <v>7.357603817094079</v>
+        <v>7.361544401944977</v>
       </c>
       <c r="N3" t="n">
-        <v>76.36157294921173</v>
+        <v>76.4730789517735</v>
       </c>
       <c r="O3" t="n">
-        <v>8.738510911431749</v>
+        <v>8.744888732955584</v>
       </c>
       <c r="P3" t="n">
-        <v>327.5762156500269</v>
+        <v>327.5108766087618</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13779,28 +13813,28 @@
         <v>0.0697</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1917868546778442</v>
+        <v>-0.1876945230719672</v>
       </c>
       <c r="J4" t="n">
+        <v>377</v>
+      </c>
+      <c r="K4" t="n">
         <v>376</v>
       </c>
-      <c r="K4" t="n">
-        <v>375</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.04413339862743204</v>
+        <v>0.04245529972984596</v>
       </c>
       <c r="M4" t="n">
-        <v>5.032682401802552</v>
+        <v>5.039075492192759</v>
       </c>
       <c r="N4" t="n">
-        <v>41.70624950017011</v>
+        <v>41.73957453443418</v>
       </c>
       <c r="O4" t="n">
-        <v>6.458037588940631</v>
+        <v>6.460617194543737</v>
       </c>
       <c r="P4" t="n">
-        <v>331.4344049461629</v>
+        <v>331.3901615554633</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13857,28 +13891,28 @@
         <v>0.0265</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05644736584794184</v>
+        <v>-0.05655691649280246</v>
       </c>
       <c r="J5" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K5" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002684960657080238</v>
+        <v>0.002711677133132362</v>
       </c>
       <c r="M5" t="n">
-        <v>5.999554452561155</v>
+        <v>5.984368202289019</v>
       </c>
       <c r="N5" t="n">
-        <v>62.55871197597397</v>
+        <v>62.39287860562066</v>
       </c>
       <c r="O5" t="n">
-        <v>7.90940655017644</v>
+        <v>7.898916293113927</v>
       </c>
       <c r="P5" t="n">
-        <v>359.6461556335574</v>
+        <v>359.6473324146531</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13916,7 +13950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F377"/>
+  <dimension ref="A1:F378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25971,6 +26005,38 @@
         </is>
       </c>
     </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>-36.7640772668679,175.75064314079307</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>-36.76476115040342,175.7503242281328</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>-36.76548438646085,175.75005002244393</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>-36.766227026483726,175.75031407718268</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0166/nzd0166.xlsx
+++ b/data/nzd0166/nzd0166.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F378"/>
+  <dimension ref="A1:F379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9502,6 +9502,30 @@
       <c r="F378" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>335.83</v>
+      </c>
+      <c r="C379" t="n">
+        <v>338.63</v>
+      </c>
+      <c r="D379" t="n">
+        <v>338.35</v>
+      </c>
+      <c r="E379" t="n">
+        <v>361.5</v>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -9516,7 +9540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B397"/>
+  <dimension ref="A1:B398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13489,6 +13513,16 @@
       </c>
       <c r="B397" t="n">
         <v>0.32</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>-0.42</v>
       </c>
     </row>
   </sheetData>
@@ -13657,28 +13691,28 @@
         <v>0.0454</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01133053127086357</v>
+        <v>-0.00883005620906723</v>
       </c>
       <c r="J2" t="n">
+        <v>378</v>
+      </c>
+      <c r="K2" t="n">
         <v>377</v>
       </c>
-      <c r="K2" t="n">
-        <v>376</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0001087907615839878</v>
+        <v>6.64201463920211e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>5.903304906317227</v>
+        <v>5.901763201975061</v>
       </c>
       <c r="N2" t="n">
-        <v>61.98390774913079</v>
+        <v>61.87349986370342</v>
       </c>
       <c r="O2" t="n">
-        <v>7.872985948744656</v>
+        <v>7.865971005775664</v>
       </c>
       <c r="P2" t="n">
-        <v>331.5995447636176</v>
+        <v>331.572439553839</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13735,28 +13769,28 @@
         <v>0.0572</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08496333241402673</v>
+        <v>-0.07757958616616928</v>
       </c>
       <c r="J3" t="n">
+        <v>378</v>
+      </c>
+      <c r="K3" t="n">
         <v>377</v>
       </c>
-      <c r="K3" t="n">
-        <v>376</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.00493428165648746</v>
+        <v>0.004117004428400017</v>
       </c>
       <c r="M3" t="n">
-        <v>7.361544401944977</v>
+        <v>7.370727376789934</v>
       </c>
       <c r="N3" t="n">
-        <v>76.4730789517735</v>
+        <v>76.74115328015033</v>
       </c>
       <c r="O3" t="n">
-        <v>8.744888732955584</v>
+        <v>8.760202810446247</v>
       </c>
       <c r="P3" t="n">
-        <v>327.5108766087618</v>
+        <v>327.4308366219377</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13813,28 +13847,28 @@
         <v>0.0697</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1876945230719672</v>
+        <v>-0.1810972332510452</v>
       </c>
       <c r="J4" t="n">
+        <v>378</v>
+      </c>
+      <c r="K4" t="n">
         <v>377</v>
       </c>
-      <c r="K4" t="n">
-        <v>376</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.04245529972984596</v>
+        <v>0.03952895663246114</v>
       </c>
       <c r="M4" t="n">
-        <v>5.039075492192759</v>
+        <v>5.057634333079736</v>
       </c>
       <c r="N4" t="n">
-        <v>41.73957453443418</v>
+        <v>42.00480540025658</v>
       </c>
       <c r="O4" t="n">
-        <v>6.460617194543737</v>
+        <v>6.481111432482594</v>
       </c>
       <c r="P4" t="n">
-        <v>331.3901615554633</v>
+        <v>331.3186467752128</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13891,28 +13925,28 @@
         <v>0.0265</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05655691649280246</v>
+        <v>-0.05471715348052095</v>
       </c>
       <c r="J5" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K5" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002711677133132362</v>
+        <v>0.002552734682535696</v>
       </c>
       <c r="M5" t="n">
-        <v>5.984368202289019</v>
+        <v>5.974061131286114</v>
       </c>
       <c r="N5" t="n">
-        <v>62.39287860562066</v>
+        <v>62.25747447604409</v>
       </c>
       <c r="O5" t="n">
-        <v>7.898916293113927</v>
+        <v>7.890340580484729</v>
       </c>
       <c r="P5" t="n">
-        <v>359.6473324146531</v>
+        <v>359.6275169120569</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13950,7 +13984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F378"/>
+  <dimension ref="A1:F379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26037,6 +26071,38 @@
         </is>
       </c>
     </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>-36.76407833463528,175.75064682787055</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>-36.76476788133519,175.75035152533079</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>-36.76548922722996,175.75010128571947</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>-36.76622655014332,175.75035382017626</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0166/nzd0166.xlsx
+++ b/data/nzd0166/nzd0166.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F379"/>
+  <dimension ref="A1:F380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9524,6 +9524,30 @@
         <v>361.5</v>
       </c>
       <c r="F379" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>334.65</v>
+      </c>
+      <c r="C380" t="n">
+        <v>336.78</v>
+      </c>
+      <c r="D380" t="n">
+        <v>335.56</v>
+      </c>
+      <c r="E380" t="n">
+        <v>361.5</v>
+      </c>
+      <c r="F380" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -9540,7 +9564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B398"/>
+  <dimension ref="A1:B399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13522,6 +13546,16 @@
         </is>
       </c>
       <c r="B398" t="n">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -13691,28 +13725,28 @@
         <v>0.0454</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.00883005620906723</v>
+        <v>-0.007011894452249674</v>
       </c>
       <c r="J2" t="n">
+        <v>379</v>
+      </c>
+      <c r="K2" t="n">
         <v>378</v>
       </c>
-      <c r="K2" t="n">
-        <v>377</v>
-      </c>
       <c r="L2" t="n">
-        <v>6.64201463920211e-05</v>
+        <v>4.21196915207922e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>5.901763201975061</v>
+        <v>5.896408448267786</v>
       </c>
       <c r="N2" t="n">
-        <v>61.87349986370342</v>
+        <v>61.73856250381845</v>
       </c>
       <c r="O2" t="n">
-        <v>7.865971005775664</v>
+        <v>7.857389038594083</v>
       </c>
       <c r="P2" t="n">
-        <v>331.572439553839</v>
+        <v>331.5526958532238</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13769,28 +13803,28 @@
         <v>0.0572</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07757958616616928</v>
+        <v>-0.07131220662289589</v>
       </c>
       <c r="J3" t="n">
+        <v>379</v>
+      </c>
+      <c r="K3" t="n">
         <v>378</v>
       </c>
-      <c r="K3" t="n">
-        <v>377</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.004117004428400017</v>
+        <v>0.003486488625410344</v>
       </c>
       <c r="M3" t="n">
-        <v>7.370727376789934</v>
+        <v>7.375656649089635</v>
       </c>
       <c r="N3" t="n">
-        <v>76.74115328015033</v>
+        <v>76.87974542027935</v>
       </c>
       <c r="O3" t="n">
-        <v>8.760202810446247</v>
+        <v>8.768109569358685</v>
       </c>
       <c r="P3" t="n">
-        <v>327.4308366219377</v>
+        <v>327.3627781750582</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13847,28 +13881,28 @@
         <v>0.0697</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1810972332510452</v>
+        <v>-0.1761194918898676</v>
       </c>
       <c r="J4" t="n">
+        <v>379</v>
+      </c>
+      <c r="K4" t="n">
         <v>378</v>
       </c>
-      <c r="K4" t="n">
-        <v>377</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.03952895663246114</v>
+        <v>0.0374997407887302</v>
       </c>
       <c r="M4" t="n">
-        <v>5.057634333079736</v>
+        <v>5.068195886902179</v>
       </c>
       <c r="N4" t="n">
-        <v>42.00480540025658</v>
+        <v>42.1091703212368</v>
       </c>
       <c r="O4" t="n">
-        <v>6.481111432482594</v>
+        <v>6.489157905401655</v>
       </c>
       <c r="P4" t="n">
-        <v>331.3186467752128</v>
+        <v>331.2645927094472</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13925,28 +13959,28 @@
         <v>0.0265</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05471715348052095</v>
+        <v>-0.05290059028187719</v>
       </c>
       <c r="J5" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="K5" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002552734682535696</v>
+        <v>0.002399737526882717</v>
       </c>
       <c r="M5" t="n">
-        <v>5.974061131286114</v>
+        <v>5.963828552520381</v>
       </c>
       <c r="N5" t="n">
-        <v>62.25747447604409</v>
+        <v>62.12231702576923</v>
       </c>
       <c r="O5" t="n">
-        <v>7.890340580484729</v>
+        <v>7.881771185829314</v>
       </c>
       <c r="P5" t="n">
-        <v>359.6275169120569</v>
+        <v>359.6079164633331</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13984,7 +14018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F379"/>
+  <dimension ref="A1:F380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26103,6 +26137,38 @@
         </is>
       </c>
     </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>-36.764074734733384,175.75063439715257</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>-36.76476299811083,175.75033172148082</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>-36.76548629756976,175.75007026087314</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>-36.76622655014332,175.75035382017626</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0166/nzd0166.xlsx
+++ b/data/nzd0166/nzd0166.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F380"/>
+  <dimension ref="A1:F382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9550,6 +9550,54 @@
       <c r="F380" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>327.75</v>
+      </c>
+      <c r="C381" t="n">
+        <v>329.51</v>
+      </c>
+      <c r="D381" t="n">
+        <v>332.2</v>
+      </c>
+      <c r="E381" t="n">
+        <v>358.15</v>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>324.54</v>
+      </c>
+      <c r="C382" t="n">
+        <v>326.88</v>
+      </c>
+      <c r="D382" t="n">
+        <v>332</v>
+      </c>
+      <c r="E382" t="n">
+        <v>359.96</v>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -9564,7 +9612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B399"/>
+  <dimension ref="A1:B401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13557,6 +13605,26 @@
       </c>
       <c r="B399" t="n">
         <v>-0.42</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>-0.57</v>
       </c>
     </row>
   </sheetData>
@@ -13725,28 +13793,28 @@
         <v>0.0454</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.007011894452249674</v>
+        <v>-0.0127453876736489</v>
       </c>
       <c r="J2" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="K2" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L2" t="n">
-        <v>4.21196915207922e-05</v>
+        <v>0.0001405205136317811</v>
       </c>
       <c r="M2" t="n">
-        <v>5.896408448267786</v>
+        <v>5.887897832175881</v>
       </c>
       <c r="N2" t="n">
-        <v>61.73856250381845</v>
+        <v>61.56827470619693</v>
       </c>
       <c r="O2" t="n">
-        <v>7.857389038594083</v>
+        <v>7.846545399486129</v>
       </c>
       <c r="P2" t="n">
-        <v>331.5526958532238</v>
+        <v>331.6154256546226</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13803,28 +13871,28 @@
         <v>0.0572</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07131220662289589</v>
+        <v>-0.06829899317106358</v>
       </c>
       <c r="J3" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="K3" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003486488625410344</v>
+        <v>0.003236527326069272</v>
       </c>
       <c r="M3" t="n">
-        <v>7.375656649089635</v>
+        <v>7.348456906933976</v>
       </c>
       <c r="N3" t="n">
-        <v>76.87974542027935</v>
+        <v>76.52319311566488</v>
       </c>
       <c r="O3" t="n">
-        <v>8.768109569358685</v>
+        <v>8.747753603963984</v>
       </c>
       <c r="P3" t="n">
-        <v>327.3627781750582</v>
+        <v>327.3298219774929</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13881,28 +13949,28 @@
         <v>0.0697</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1761194918898676</v>
+        <v>-0.1700162161947314</v>
       </c>
       <c r="J4" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="K4" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0374997407887302</v>
+        <v>0.03532425590026711</v>
       </c>
       <c r="M4" t="n">
-        <v>5.068195886902179</v>
+        <v>5.070298954935252</v>
       </c>
       <c r="N4" t="n">
-        <v>42.1091703212368</v>
+        <v>42.04754786473653</v>
       </c>
       <c r="O4" t="n">
-        <v>6.489157905401655</v>
+        <v>6.484408058160477</v>
       </c>
       <c r="P4" t="n">
-        <v>331.2645927094472</v>
+        <v>331.1978265092342</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13959,28 +14027,28 @@
         <v>0.0265</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05290059028187719</v>
+        <v>-0.05195583249089629</v>
       </c>
       <c r="J5" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="K5" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002399737526882717</v>
+        <v>0.002343189507416632</v>
       </c>
       <c r="M5" t="n">
-        <v>5.963828552520381</v>
+        <v>5.935584343157369</v>
       </c>
       <c r="N5" t="n">
-        <v>62.12231702576923</v>
+        <v>61.80437885622684</v>
       </c>
       <c r="O5" t="n">
-        <v>7.881771185829314</v>
+        <v>7.861576105096664</v>
       </c>
       <c r="P5" t="n">
-        <v>359.6079164633331</v>
+        <v>359.597641956987</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14018,7 +14086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F380"/>
+  <dimension ref="A1:F382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26169,6 +26237,70 @@
         </is>
       </c>
     </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>-36.764053684432575,175.7505617090777</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>-36.76474380832582,175.7502538977253</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>-36.76548276936595,175.7500328976198</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>-36.76622699964802,175.7503163162246</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>-36.76404389145081,175.7505278933338</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>-36.764736866203556,175.75022574416096</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>-36.76548255935345,175.75003067361672</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>-36.76622675678277,175.75033657955385</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0166/nzd0166.xlsx
+++ b/data/nzd0166/nzd0166.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F382"/>
+  <dimension ref="A1:F383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9596,6 +9596,30 @@
         <v>359.96</v>
       </c>
       <c r="F382" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>325.45</v>
+      </c>
+      <c r="C383" t="n">
+        <v>328.58</v>
+      </c>
+      <c r="D383" t="n">
+        <v>333.39</v>
+      </c>
+      <c r="E383" t="n">
+        <v>362.86</v>
+      </c>
+      <c r="F383" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -9612,7 +9636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B401"/>
+  <dimension ref="A1:B402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13625,6 +13649,16 @@
       </c>
       <c r="B401" t="n">
         <v>-0.57</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>-0.55</v>
       </c>
     </row>
   </sheetData>
@@ -13793,28 +13827,28 @@
         <v>0.0454</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0127453876736489</v>
+        <v>-0.01592807594598961</v>
       </c>
       <c r="J2" t="n">
+        <v>382</v>
+      </c>
+      <c r="K2" t="n">
         <v>381</v>
       </c>
-      <c r="K2" t="n">
-        <v>380</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0001405205136317811</v>
+        <v>0.0002204752198299298</v>
       </c>
       <c r="M2" t="n">
-        <v>5.887897832175881</v>
+        <v>5.885039891482616</v>
       </c>
       <c r="N2" t="n">
-        <v>61.56827470619693</v>
+        <v>61.49488710570705</v>
       </c>
       <c r="O2" t="n">
-        <v>7.846545399486129</v>
+        <v>7.841867577669688</v>
       </c>
       <c r="P2" t="n">
-        <v>331.6154256546226</v>
+        <v>331.6503175121414</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13871,28 +13905,28 @@
         <v>0.0572</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.06829899317106358</v>
+        <v>-0.06661385254100904</v>
       </c>
       <c r="J3" t="n">
+        <v>382</v>
+      </c>
+      <c r="K3" t="n">
         <v>381</v>
       </c>
-      <c r="K3" t="n">
-        <v>380</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.003236527326069272</v>
+        <v>0.003097116064452066</v>
       </c>
       <c r="M3" t="n">
-        <v>7.348456906933976</v>
+        <v>7.335650985857909</v>
       </c>
       <c r="N3" t="n">
-        <v>76.52319311566488</v>
+        <v>76.34707327307522</v>
       </c>
       <c r="O3" t="n">
-        <v>8.747753603963984</v>
+        <v>8.737681229770015</v>
       </c>
       <c r="P3" t="n">
-        <v>327.3298219774929</v>
+        <v>327.3113477564157</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13949,28 +13983,28 @@
         <v>0.0697</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1700162161947314</v>
+        <v>-0.1663183926707062</v>
       </c>
       <c r="J4" t="n">
+        <v>382</v>
+      </c>
+      <c r="K4" t="n">
         <v>381</v>
       </c>
-      <c r="K4" t="n">
-        <v>380</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.03532425590026711</v>
+        <v>0.0339634182388886</v>
       </c>
       <c r="M4" t="n">
-        <v>5.070298954935252</v>
+        <v>5.074305905082141</v>
       </c>
       <c r="N4" t="n">
-        <v>42.04754786473653</v>
+        <v>42.05626077027024</v>
       </c>
       <c r="O4" t="n">
-        <v>6.484408058160477</v>
+        <v>6.4850798584343</v>
       </c>
       <c r="P4" t="n">
-        <v>331.1978265092342</v>
+        <v>331.1572872165076</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14027,28 +14061,28 @@
         <v>0.0265</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05195583249089629</v>
+        <v>-0.04942824467726014</v>
       </c>
       <c r="J5" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K5" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002343189507416632</v>
+        <v>0.002132204062068377</v>
       </c>
       <c r="M5" t="n">
-        <v>5.935584343157369</v>
+        <v>5.927735632117752</v>
       </c>
       <c r="N5" t="n">
-        <v>61.80437885622684</v>
+        <v>61.69901701815756</v>
       </c>
       <c r="O5" t="n">
-        <v>7.861576105096664</v>
+        <v>7.854872183438605</v>
       </c>
       <c r="P5" t="n">
-        <v>359.597641956987</v>
+        <v>359.570106595749</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14086,7 +14120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F382"/>
+  <dimension ref="A1:F383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26301,6 +26335,38 @@
         </is>
       </c>
     </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>-36.76404666765539,175.75053747972768</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>-36.764741353507716,175.75024394228186</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>-36.765484018939496,175.7500461304384</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>-36.76622636765447,175.75036904566076</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
